--- a/PARCEIROS.xlsx
+++ b/PARCEIROS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Samuel\Desktop\CONSULT\MY CERT\PROJETO FABIO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Samuel\Desktop\CONSULT\MY CERT\PROJETO FABIO\outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{019AC992-0D42-414E-9782-F68494253F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F80FB9BA-F55D-4A61-AF46-562E17E28339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
   <si>
     <t>PARCEIRO</t>
   </si>
@@ -95,6 +95,18 @@
   </si>
   <si>
     <t>GIGAPEL INFORMATICA, ESCRITORIO E PAPELARIA LTDA</t>
+  </si>
+  <si>
+    <t>COMPLANO CONTABILIDADE LTDA</t>
+  </si>
+  <si>
+    <t>Michael Fernandes da Silva</t>
+  </si>
+  <si>
+    <t>60.507.711 JANAINA OLIVEIRA DA COSTA REIS BARBOSA</t>
+  </si>
+  <si>
+    <t>VALDIRENE ANTUNES DA SILVA</t>
   </si>
 </sst>
 </file>
@@ -571,7 +583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CC52216-1900-4EF5-99F5-6295DAE9AD9C}">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="69.21875" customWidth="1"/>
@@ -763,8 +775,33 @@
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="9"/>
-      <c r="B24" s="10"/>
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="1">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:B21" xr:uid="{7CC52216-1900-4EF5-99F5-6295DAE9AD9C}"/>

--- a/PARCEIROS.xlsx
+++ b/PARCEIROS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Samuel\Desktop\CONSULT\MY CERT\PROJETO FABIO\outputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Samuel\Desktop\CONSULT\MY CERT\GITHUB PROJETO FABIO\outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F80FB9BA-F55D-4A61-AF46-562E17E28339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79E8D714-4388-4E06-9725-F6DF133C6D90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
   <si>
     <t>PARCEIRO</t>
   </si>
@@ -107,6 +107,9 @@
   </si>
   <si>
     <t>VALDIRENE ANTUNES DA SILVA</t>
+  </si>
+  <si>
+    <t>W H DOS SANTOS CONTABILIDADE</t>
   </si>
 </sst>
 </file>
@@ -583,7 +586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CC52216-1900-4EF5-99F5-6295DAE9AD9C}">
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="69.21875" customWidth="1"/>
@@ -802,6 +805,14 @@
       <c r="A27" t="s">
         <v>27</v>
       </c>
+      <c r="B27" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:B21" xr:uid="{7CC52216-1900-4EF5-99F5-6295DAE9AD9C}"/>
